--- a/doc/board/water-leak/gerbers/Folder Structure - 27.04.2025 22-26-38/Bill of Materials-water-leak.xlsx
+++ b/doc/board/water-leak/gerbers/Folder Structure - 27.04.2025 22-26-38/Bill of Materials-water-leak.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrey\git\smart.roof\leaksensor\doc\board\water-leak\Project Outputs for water-leak\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrey\git\smart.roof\leaksensor\doc\board\water-leak\gerbers\Folder Structure - 27.04.2025 22-26-38\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C781925A-94CA-4B51-8EE9-4D9472A01766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{011DAF86-364D-4378-9E9A-2AE5AAA1A845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="720" windowWidth="28800" windowHeight="15370" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="484" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="370">
   <si>
     <t>Bill of Materials</t>
   </si>
@@ -1549,6 +1549,85 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>28575</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1408115</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>12700</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{375E4432-10DF-4A33-8902-892C277ED9BA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="10607675" y="285750"/>
+          <a:ext cx="1379540" cy="285750"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:miter lim="800000"/>
+              <a:headEnd/>
+              <a:tailEnd/>
+            </a14:hiddenLine>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -4517,10 +4596,938 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:B124"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="44.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="3"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="31"/>
+      <c r="B2" s="6"/>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="10"/>
+      <c r="B3" s="8"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="10"/>
+      <c r="B4" s="8"/>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="10"/>
+      <c r="B5" s="8"/>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="10"/>
+      <c r="B6" s="8"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="10"/>
+      <c r="B7" s="9"/>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="10"/>
+      <c r="B8" s="9"/>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="10"/>
+      <c r="B9" s="9"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="10"/>
+      <c r="B10" s="9"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="34" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="32" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="32" t="s">
+        <v>25</v>
+      </c>
+      <c r="B15" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="32" t="s">
+        <v>27</v>
+      </c>
+      <c r="B17" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="32" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B23" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="B24" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B25" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B26" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A33" s="32" t="s">
+        <v>42</v>
+      </c>
+      <c r="B33" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A34" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B34" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A35" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="B35" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A36" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="B36" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A37" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="B37" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A38" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="B38" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A39" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A40" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="B40" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A41" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="B41" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A42" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B42" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A43" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B43" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A44" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A45" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="B45" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A46" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="B46" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A47" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A48" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="B48" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A49" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A50" s="32" t="s">
+        <v>58</v>
+      </c>
+      <c r="B50" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A51" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="B51" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A52" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="B52" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A53" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="B53" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A54" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="B54" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A55" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B55" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A56" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="B56" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A57" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="B57" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A58" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="B58" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A59" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="B59" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A60" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="B60" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A61" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="B61" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A62" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="B62" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A63" s="32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B63" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A64" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="B64" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A65" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A66" s="32" t="s">
+        <v>74</v>
+      </c>
+      <c r="B66" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A67" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="B67" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A68" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="B68" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A69" s="32" t="s">
+        <v>77</v>
+      </c>
+      <c r="B69" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A70" s="32" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A71" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A72" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A73" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A74" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="B74" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A75" s="32" t="s">
+        <v>83</v>
+      </c>
+      <c r="B75" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A76" s="32" t="s">
+        <v>84</v>
+      </c>
+      <c r="B76" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A77" s="32">
+        <v>7447715470</v>
+      </c>
+      <c r="B77" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A78" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="B78" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A79" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="B79" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A80" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="B80" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A81" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="B81" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A82" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="B82" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A83" s="32" t="s">
+        <v>90</v>
+      </c>
+      <c r="B83" s="16">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A84" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="B84" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A85" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B85" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A86" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="B86" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A87" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="B87" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A88" s="32" t="s">
+        <v>95</v>
+      </c>
+      <c r="B88" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A89" s="32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B89" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A90" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="B90" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A91" s="32" t="s">
+        <v>98</v>
+      </c>
+      <c r="B91" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A92" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="B92" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A93" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="B93" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A94" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="B94" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A95" s="32" t="s">
+        <v>102</v>
+      </c>
+      <c r="B95" s="16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A96" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="B96" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A97" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="B97" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A98" s="32" t="s">
+        <v>105</v>
+      </c>
+      <c r="B98" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A99" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B99" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A100" s="32" t="s">
+        <v>107</v>
+      </c>
+      <c r="B100" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A101" s="32" t="s">
+        <v>108</v>
+      </c>
+      <c r="B101" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A102" s="32" t="s">
+        <v>109</v>
+      </c>
+      <c r="B102" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A103" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B103" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A104" s="32" t="s">
+        <v>111</v>
+      </c>
+      <c r="B104" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A105" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B105" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A106" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="B106" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A107" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B107" s="16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A108" s="32" t="s">
+        <v>115</v>
+      </c>
+      <c r="B108" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A109" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B109" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A110" s="32" t="s">
+        <v>117</v>
+      </c>
+      <c r="B110" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A111" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B111" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A112" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B112" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A113" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B113" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A114" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="B114" s="16">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A115" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B115" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A116" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="B116" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A117" s="33"/>
+      <c r="B117" s="17">
+        <f>SUM(B13:B116)</f>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B118" s="20"/>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A119" s="31" t="s">
+        <v>7</v>
+      </c>
+      <c r="B119" s="21"/>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A120" s="10"/>
+      <c r="B120" s="22"/>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A121" s="10"/>
+      <c r="B121" s="22"/>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A122" s="10"/>
+      <c r="B122" s="22"/>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A123" s="10"/>
+      <c r="B123" s="22"/>
+    </row>
+    <row r="124" spans="1:2" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A124" s="12"/>
+      <c r="B124" s="23"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
